--- a/APM_files/153101365/Expedia Update Request per May 18, 2026.xlsx
+++ b/APM_files/153101365/Expedia Update Request per May 18, 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Dev/workspace/APM_files/153101365/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A638590468D67AC663FDCE6303A629604A8C2A06" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78A851F-02D6-DB4C-AA75-E2993BD8E0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30280" yWindow="6340" windowWidth="15120" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Sold Removal" sheetId="1" r:id="rId1"/>
@@ -992,7 +992,7 @@
     <col min="2" max="2" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
